--- a/2030.xlsx
+++ b/2030.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="53">
   <si>
     <t xml:space="preserve">Power Generation</t>
   </si>
@@ -165,6 +165,12 @@
   </si>
   <si>
     <t xml:space="preserve">Ccn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fosil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fosiln</t>
   </si>
   <si>
     <t xml:space="preserve">Solarn</t>
@@ -180,10 +186,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* \-??_-;_-@_-"/>
     <numFmt numFmtId="166" formatCode="_ * #,##0.000_ ;_ * \-#,##0.000_ ;_ * \-??_ ;_ @_ "/>
+    <numFmt numFmtId="167" formatCode="0.00"/>
   </numFmts>
   <fonts count="4">
     <font>
@@ -265,7 +272,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -283,6 +290,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="3" borderId="0" xfId="15" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -364,7 +375,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:Z22"/>
-  <sheetFormatPr defaultColWidth="10.72265625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="10.7421875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="21.82"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="2" style="0" width="10.12"/>
@@ -1824,8 +1835,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B2:M26"/>
-  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="B2:O54"/>
+  <sheetFormatPr defaultColWidth="11.58984375" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="0" t="s">
@@ -1847,22 +1858,28 @@
         <v>47</v>
       </c>
       <c r="H2" s="0" t="s">
+        <v>48</v>
+      </c>
+      <c r="I2" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="J2" s="0" t="s">
         <v>42</v>
       </c>
-      <c r="I2" s="0" t="s">
-        <v>48</v>
-      </c>
-      <c r="J2" s="0" t="s">
+      <c r="K2" s="0" t="s">
+        <v>50</v>
+      </c>
+      <c r="L2" s="0" t="s">
         <v>43</v>
       </c>
-      <c r="K2" s="0" t="s">
-        <v>49</v>
-      </c>
-      <c r="L2" s="0" t="s">
+      <c r="M2" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="N2" s="0" t="s">
         <v>44</v>
       </c>
-      <c r="M2" s="0" t="s">
-        <v>50</v>
+      <c r="O2" s="0" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1885,10 +1902,12 @@
         <v>-0.00011704270800692</v>
       </c>
       <c r="H3" s="0" t="n">
+        <f aca="false">C3+E3</f>
         <v>0</v>
       </c>
       <c r="I3" s="0" t="n">
-        <v>0</v>
+        <f aca="false">D3+F3+G3</f>
+        <v>-0.00011704270800692</v>
       </c>
       <c r="J3" s="0" t="n">
         <v>0</v>
@@ -1900,6 +1919,12 @@
         <v>0</v>
       </c>
       <c r="M3" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" s="0" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1923,10 +1948,12 @@
         <v>-0.000117042708152439</v>
       </c>
       <c r="H4" s="0" t="n">
-        <v>0</v>
+        <f aca="false">C4+E4</f>
+        <v>0.0001170427080433</v>
       </c>
       <c r="I4" s="0" t="n">
-        <v>0</v>
+        <f aca="false">D4+F4+G4</f>
+        <v>-0.000117042708152439</v>
       </c>
       <c r="J4" s="0" t="n">
         <v>0</v>
@@ -1938,6 +1965,12 @@
         <v>0</v>
       </c>
       <c r="M4" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" s="0" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1961,10 +1994,12 @@
         <v>-0.00440753648296231</v>
       </c>
       <c r="H5" s="0" t="n">
+        <f aca="false">C5+E5</f>
         <v>0</v>
       </c>
       <c r="I5" s="0" t="n">
-        <v>0</v>
+        <f aca="false">D5+F5+G5</f>
+        <v>-0.00601735714855567</v>
       </c>
       <c r="J5" s="0" t="n">
         <v>0</v>
@@ -1976,6 +2011,12 @@
         <v>0</v>
       </c>
       <c r="M5" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" s="0" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1999,10 +2040,12 @@
         <v>-22.4817525509589</v>
       </c>
       <c r="H6" s="0" t="n">
+        <f aca="false">C6+E6</f>
         <v>0</v>
       </c>
       <c r="I6" s="0" t="n">
-        <v>0</v>
+        <f aca="false">D6+F6+G6</f>
+        <v>-22.6613670215064</v>
       </c>
       <c r="J6" s="0" t="n">
         <v>0</v>
@@ -2014,6 +2057,12 @@
         <v>0</v>
       </c>
       <c r="M6" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" s="0" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2037,21 +2086,29 @@
         <v>-63.4416593061372</v>
       </c>
       <c r="H7" s="0" t="n">
+        <f aca="false">C7+E7</f>
         <v>0</v>
       </c>
       <c r="I7" s="0" t="n">
-        <v>0</v>
+        <f aca="false">D7+F7+G7</f>
+        <v>-64.4324482097893</v>
       </c>
       <c r="J7" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" s="0" t="n">
         <v>8.419203</v>
       </c>
-      <c r="K7" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" s="0" t="n">
-        <v>0</v>
-      </c>
       <c r="M7" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" s="0" t="n">
         <v>-68.9913321945572</v>
       </c>
     </row>
@@ -2075,21 +2132,29 @@
         <v>-91.3827781866</v>
       </c>
       <c r="H8" s="0" t="n">
+        <f aca="false">C8+E8</f>
         <v>0</v>
       </c>
       <c r="I8" s="0" t="n">
+        <f aca="false">D8+F8+G8</f>
+        <v>-92.8099325769869</v>
+      </c>
+      <c r="J8" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" s="0" t="n">
         <v>-33.9250813405539</v>
       </c>
-      <c r="J8" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" s="0" t="n">
-        <v>0</v>
-      </c>
       <c r="L8" s="0" t="n">
         <v>0</v>
       </c>
       <c r="M8" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" s="0" t="n">
         <v>-53.3243618016254</v>
       </c>
     </row>
@@ -2113,14 +2178,16 @@
         <v>-92.6939261715745</v>
       </c>
       <c r="H9" s="0" t="n">
+        <f aca="false">C9+E9</f>
+        <v>0</v>
+      </c>
+      <c r="I9" s="0" t="n">
+        <f aca="false">D9+F9+G9</f>
+        <v>-94.1415571839282</v>
+      </c>
+      <c r="J9" s="0" t="n">
         <v>22.2700366763001</v>
       </c>
-      <c r="I9" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" s="0" t="n">
-        <v>0</v>
-      </c>
       <c r="K9" s="0" t="n">
         <v>0</v>
       </c>
@@ -2128,6 +2195,12 @@
         <v>0</v>
       </c>
       <c r="M9" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" s="0" t="n">
         <v>-110.771323260276</v>
       </c>
     </row>
@@ -2151,14 +2224,16 @@
         <v>-71.3461590132311</v>
       </c>
       <c r="H10" s="0" t="n">
+        <f aca="false">C10+E10</f>
+        <v>0</v>
+      </c>
+      <c r="I10" s="0" t="n">
+        <f aca="false">D10+F10+G10</f>
+        <v>-72.4603950442813</v>
+      </c>
+      <c r="J10" s="0" t="n">
         <v>58.41</v>
       </c>
-      <c r="I10" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" s="0" t="n">
-        <v>0</v>
-      </c>
       <c r="K10" s="0" t="n">
         <v>0</v>
       </c>
@@ -2166,6 +2241,12 @@
         <v>0</v>
       </c>
       <c r="M10" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" s="0" t="n">
         <v>-126.529100423132</v>
       </c>
     </row>
@@ -2189,21 +2270,29 @@
         <v>-22.5336931447532</v>
       </c>
       <c r="H11" s="0" t="n">
+        <f aca="false">C11+E11</f>
         <v>0</v>
       </c>
       <c r="I11" s="0" t="n">
+        <f aca="false">D11+F11+G11</f>
+        <v>-22.8856091155885</v>
+      </c>
+      <c r="J11" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" s="0" t="n">
         <v>-18.45</v>
       </c>
-      <c r="J11" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" s="0" t="n">
-        <v>0</v>
-      </c>
       <c r="L11" s="0" t="n">
         <v>0</v>
       </c>
       <c r="M11" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" s="0" t="n">
         <v>-3.06447152111973</v>
       </c>
     </row>
@@ -2227,10 +2316,12 @@
         <v>-0.0295250776053581</v>
       </c>
       <c r="H12" s="0" t="n">
+        <f aca="false">C12+E12</f>
         <v>0</v>
       </c>
       <c r="I12" s="0" t="n">
-        <v>0</v>
+        <f aca="false">D12+F12+G12</f>
+        <v>-0.0299861802875785</v>
       </c>
       <c r="J12" s="0" t="n">
         <v>0</v>
@@ -2242,6 +2333,12 @@
         <v>0</v>
       </c>
       <c r="M12" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" s="0" t="n">
         <v>-0.0281896286248084</v>
       </c>
     </row>
@@ -2265,21 +2362,29 @@
         <v>-0.00406779099852429</v>
       </c>
       <c r="H13" s="0" t="n">
+        <f aca="false">C13+E13</f>
         <v>0</v>
       </c>
       <c r="I13" s="0" t="n">
-        <v>0</v>
+        <f aca="false">D13+F13+G13</f>
+        <v>-0.00413131900563531</v>
       </c>
       <c r="J13" s="0" t="n">
         <v>0</v>
       </c>
       <c r="K13" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" s="0" t="n">
         <v>-13.33543185</v>
       </c>
-      <c r="L13" s="0" t="n">
+      <c r="N13" s="0" t="n">
         <v>13.3315480492835</v>
       </c>
-      <c r="M13" s="0" t="n">
+      <c r="O13" s="0" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2303,10 +2408,12 @@
         <v>-1.20053300634027E-013</v>
       </c>
       <c r="H14" s="0" t="n">
-        <v>0</v>
+        <f aca="false">C14+E14</f>
+        <v>9.09494701772928E-015</v>
       </c>
       <c r="I14" s="0" t="n">
-        <v>0</v>
+        <f aca="false">D14+F14+G14</f>
+        <v>-1.20053300634027E-013</v>
       </c>
       <c r="J14" s="0" t="n">
         <v>0</v>
@@ -2318,6 +2425,12 @@
         <v>0</v>
       </c>
       <c r="M14" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" s="0" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2341,21 +2454,29 @@
         <v>0</v>
       </c>
       <c r="H15" s="0" t="n">
+        <f aca="false">C15+E15</f>
         <v>0</v>
       </c>
       <c r="I15" s="0" t="n">
+        <f aca="false">D15+F15+G15</f>
         <v>0</v>
       </c>
       <c r="J15" s="0" t="n">
         <v>0</v>
       </c>
       <c r="K15" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" s="0" t="n">
         <v>-7.9850106</v>
       </c>
-      <c r="L15" s="0" t="n">
+      <c r="N15" s="0" t="n">
         <v>7.98501060000007</v>
       </c>
-      <c r="M15" s="0" t="n">
+      <c r="O15" s="0" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2379,10 +2500,12 @@
         <v>-1.16415321826935E-013</v>
       </c>
       <c r="H16" s="0" t="n">
+        <f aca="false">C16+E16</f>
         <v>0</v>
       </c>
       <c r="I16" s="0" t="n">
-        <v>0</v>
+        <f aca="false">D16+F16+G16</f>
+        <v>-1.16415321826935E-013</v>
       </c>
       <c r="J16" s="0" t="n">
         <v>0</v>
@@ -2394,6 +2517,12 @@
         <v>0</v>
       </c>
       <c r="M16" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" s="0" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2417,10 +2546,12 @@
         <v>-0.0382848694297136</v>
       </c>
       <c r="H17" s="0" t="n">
+        <f aca="false">C17+E17</f>
         <v>0</v>
       </c>
       <c r="I17" s="0" t="n">
-        <v>0</v>
+        <f aca="false">D17+F17+G17</f>
+        <v>-0.0388827766128343</v>
       </c>
       <c r="J17" s="0" t="n">
         <v>0</v>
@@ -2432,6 +2563,12 @@
         <v>0</v>
       </c>
       <c r="M17" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" s="0" t="n">
         <v>-0.0365532062465661</v>
       </c>
     </row>
@@ -2455,10 +2592,12 @@
         <v>-14.5291265754794</v>
       </c>
       <c r="H18" s="0" t="n">
+        <f aca="false">C18+E18</f>
         <v>0</v>
       </c>
       <c r="I18" s="0" t="n">
-        <v>0</v>
+        <f aca="false">D18+F18+G18</f>
+        <v>-14.756032642379</v>
       </c>
       <c r="J18" s="0" t="n">
         <v>0</v>
@@ -2470,6 +2609,12 @@
         <v>0</v>
       </c>
       <c r="M18" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" s="0" t="n">
         <v>-13.8719595552709</v>
       </c>
     </row>
@@ -2493,21 +2638,29 @@
         <v>-64.2054893969044</v>
       </c>
       <c r="H19" s="0" t="n">
+        <f aca="false">C19+E19</f>
         <v>0</v>
       </c>
       <c r="I19" s="0" t="n">
+        <f aca="false">D19+F19+G19</f>
+        <v>-65.2082072820252</v>
+      </c>
+      <c r="J19" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" s="0" t="n">
         <v>-21.9525841300541</v>
       </c>
-      <c r="J19" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" s="0" t="n">
-        <v>0</v>
-      </c>
       <c r="L19" s="0" t="n">
         <v>0</v>
       </c>
       <c r="M19" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" s="0" t="n">
         <v>-39.3488263513843</v>
       </c>
     </row>
@@ -2531,21 +2684,29 @@
         <v>-89.7039078479602</v>
       </c>
       <c r="H20" s="0" t="n">
+        <f aca="false">C20+E20</f>
         <v>0</v>
       </c>
       <c r="I20" s="0" t="n">
+        <f aca="false">D20+F20+G20</f>
+        <v>-91.1048427775009</v>
+      </c>
+      <c r="J20" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" s="0" t="n">
         <v>-45.4971228461346</v>
       </c>
-      <c r="J20" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" s="0" t="n">
-        <v>0</v>
-      </c>
       <c r="L20" s="0" t="n">
         <v>0</v>
       </c>
       <c r="M20" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" s="0" t="n">
         <v>-40.1493869527933</v>
       </c>
     </row>
@@ -2569,21 +2730,29 @@
         <v>-87.2937616921694</v>
       </c>
       <c r="H21" s="0" t="n">
+        <f aca="false">C21+E21</f>
         <v>0</v>
       </c>
       <c r="I21" s="0" t="n">
+        <f aca="false">D21+F21+G21</f>
+        <v>-88.6570565900109</v>
+      </c>
+      <c r="J21" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" s="0" t="n">
         <v>-199.065316647012</v>
       </c>
-      <c r="J21" s="0" t="n">
+      <c r="L21" s="0" t="n">
         <v>11.5897266</v>
       </c>
-      <c r="K21" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" s="0" t="n">
+      <c r="M21" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" s="0" t="n">
         <v>104.130213067165</v>
       </c>
-      <c r="M21" s="0" t="n">
+      <c r="O21" s="0" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2607,21 +2776,29 @@
         <v>-68.6418402251867</v>
       </c>
       <c r="H22" s="0" t="n">
+        <f aca="false">C22+E22</f>
         <v>0</v>
       </c>
       <c r="I22" s="0" t="n">
-        <v>0</v>
+        <f aca="false">D22+F22+G22</f>
+        <v>-69.7138420354356</v>
       </c>
       <c r="J22" s="0" t="n">
         <v>0</v>
       </c>
       <c r="K22" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" s="0" t="n">
         <v>-12.9350691</v>
       </c>
-      <c r="L22" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" s="0" t="n">
+      <c r="N22" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" s="0" t="n">
         <v>-52.6020315960714</v>
       </c>
     </row>
@@ -2645,21 +2822,29 @@
         <v>-26.936839236199</v>
       </c>
       <c r="H23" s="0" t="n">
+        <f aca="false">C23+E23</f>
         <v>0</v>
       </c>
       <c r="I23" s="0" t="n">
+        <f aca="false">D23+F23+G23</f>
+        <v>-27.3575205630524</v>
+      </c>
+      <c r="J23" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" s="0" t="n">
         <v>-16.9182</v>
       </c>
-      <c r="J23" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" s="0" t="n">
-        <v>0</v>
-      </c>
       <c r="L23" s="0" t="n">
         <v>0</v>
       </c>
       <c r="M23" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" s="0" t="n">
         <v>-8.80025888258852</v>
       </c>
     </row>
@@ -2683,21 +2868,29 @@
         <v>-0.759575286532199</v>
       </c>
       <c r="H24" s="0" t="n">
+        <f aca="false">C24+E24</f>
+        <v>0</v>
+      </c>
+      <c r="I24" s="0" t="n">
+        <f aca="false">D24+F24+G24</f>
+        <v>-0.771437819347626</v>
+      </c>
+      <c r="J24" s="0" t="n">
         <v>0.732</v>
       </c>
-      <c r="I24" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" s="0" t="n">
-        <v>0</v>
-      </c>
       <c r="K24" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" s="0" t="n">
         <v>-12.081843</v>
       </c>
-      <c r="L24" s="0" t="n">
+      <c r="N24" s="0" t="n">
         <v>10.6246240682761</v>
       </c>
-      <c r="M24" s="0" t="n">
+      <c r="O24" s="0" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2721,21 +2914,29 @@
         <v>0</v>
       </c>
       <c r="H25" s="0" t="n">
+        <f aca="false">C25+E25</f>
         <v>0</v>
       </c>
       <c r="I25" s="0" t="n">
+        <f aca="false">D25+F25+G25</f>
         <v>0</v>
       </c>
       <c r="J25" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" s="0" t="n">
         <v>10.8095706</v>
       </c>
-      <c r="K25" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" s="0" t="n">
-        <v>0</v>
-      </c>
       <c r="M25" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" s="0" t="n">
         <v>-10.8095705999999</v>
       </c>
     </row>
@@ -2759,21 +2960,754 @@
         <v>0</v>
       </c>
       <c r="H26" s="0" t="n">
+        <f aca="false">C26+E26</f>
         <v>0</v>
       </c>
       <c r="I26" s="0" t="n">
+        <f aca="false">D26+F26+G26</f>
         <v>0</v>
       </c>
       <c r="J26" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" s="0" t="n">
         <v>9.25891965</v>
       </c>
-      <c r="K26" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="L26" s="0" t="n">
-        <v>0</v>
-      </c>
       <c r="M26" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" s="0" t="n">
+        <v>-9.25891964999985</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F30" s="0" t="s">
+        <v>38</v>
+      </c>
+      <c r="G30" s="0" t="s">
+        <v>48</v>
+      </c>
+      <c r="H30" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="I30" s="0" t="s">
+        <v>42</v>
+      </c>
+      <c r="J30" s="0" t="s">
+        <v>50</v>
+      </c>
+      <c r="K30" s="0" t="s">
+        <v>43</v>
+      </c>
+      <c r="L30" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="M30" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="N30" s="0" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F31" s="0" t="s">
+        <v>5</v>
+      </c>
+      <c r="G31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" s="5" t="n">
+        <v>-0.00011704270800692</v>
+      </c>
+      <c r="I31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F32" s="0" t="s">
+        <v>6</v>
+      </c>
+      <c r="G32" s="5" t="n">
+        <v>0.0001170427080433</v>
+      </c>
+      <c r="H32" s="5" t="n">
+        <v>-0.000117042708152439</v>
+      </c>
+      <c r="I32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F33" s="0" t="s">
+        <v>7</v>
+      </c>
+      <c r="G33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" s="5" t="n">
+        <v>-0.00601735714855567</v>
+      </c>
+      <c r="I33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F34" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="G34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" s="5" t="n">
+        <v>-22.6613670215064</v>
+      </c>
+      <c r="I34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F35" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="G35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" s="5" t="n">
+        <v>-64.4324482097893</v>
+      </c>
+      <c r="I35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" s="5" t="n">
+        <v>8.419203</v>
+      </c>
+      <c r="L35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" s="5" t="n">
+        <v>-68.9913321945572</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F36" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="G36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" s="5" t="n">
+        <v>-92.8099325769869</v>
+      </c>
+      <c r="I36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" s="5" t="n">
+        <v>-33.9250813405539</v>
+      </c>
+      <c r="K36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" s="5" t="n">
+        <v>-53.3243618016254</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F37" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="G37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" s="5" t="n">
+        <v>-94.1415571839282</v>
+      </c>
+      <c r="I37" s="5" t="n">
+        <v>22.2700366763001</v>
+      </c>
+      <c r="J37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" s="5" t="n">
+        <v>-110.771323260276</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F38" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="G38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" s="5" t="n">
+        <v>-72.4603950442813</v>
+      </c>
+      <c r="I38" s="5" t="n">
+        <v>58.41</v>
+      </c>
+      <c r="J38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" s="5" t="n">
+        <v>-126.529100423132</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F39" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="G39" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" s="5" t="n">
+        <v>-22.8856091155885</v>
+      </c>
+      <c r="I39" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" s="5" t="n">
+        <v>-18.45</v>
+      </c>
+      <c r="K39" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" s="5" t="n">
+        <v>-3.06447152111973</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F40" s="0" t="s">
+        <v>14</v>
+      </c>
+      <c r="G40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" s="5" t="n">
+        <v>-0.0299861802875785</v>
+      </c>
+      <c r="I40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N40" s="5" t="n">
+        <v>-0.0281896286248084</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F41" s="0" t="s">
+        <v>15</v>
+      </c>
+      <c r="G41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" s="5" t="n">
+        <v>-0.00413131900563531</v>
+      </c>
+      <c r="I41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" s="5" t="n">
+        <v>-13.33543185</v>
+      </c>
+      <c r="M41" s="5" t="n">
+        <v>13.3315480492835</v>
+      </c>
+      <c r="N41" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F42" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="G42" s="5" t="n">
+        <v>9.09494701772928E-015</v>
+      </c>
+      <c r="H42" s="5" t="n">
+        <v>-1.20053300634027E-013</v>
+      </c>
+      <c r="I42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N42" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F43" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="G43" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K43" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" s="5" t="n">
+        <v>-7.9850106</v>
+      </c>
+      <c r="M43" s="5" t="n">
+        <v>7.98501060000007</v>
+      </c>
+      <c r="N43" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F44" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="G44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" s="5" t="n">
+        <v>-1.16415321826935E-013</v>
+      </c>
+      <c r="I44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N44" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F45" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="G45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" s="5" t="n">
+        <v>-0.0388827766128343</v>
+      </c>
+      <c r="I45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N45" s="5" t="n">
+        <v>-0.0365532062465661</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F46" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="G46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" s="5" t="n">
+        <v>-14.756032642379</v>
+      </c>
+      <c r="I46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N46" s="5" t="n">
+        <v>-13.8719595552709</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F47" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="G47" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" s="5" t="n">
+        <v>-65.2082072820252</v>
+      </c>
+      <c r="I47" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J47" s="5" t="n">
+        <v>-21.9525841300541</v>
+      </c>
+      <c r="K47" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L47" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M47" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N47" s="5" t="n">
+        <v>-39.3488263513843</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F48" s="0" t="s">
+        <v>22</v>
+      </c>
+      <c r="G48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" s="5" t="n">
+        <v>-91.1048427775009</v>
+      </c>
+      <c r="I48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J48" s="5" t="n">
+        <v>-45.4971228461346</v>
+      </c>
+      <c r="K48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N48" s="5" t="n">
+        <v>-40.1493869527933</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F49" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="G49" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" s="5" t="n">
+        <v>-88.6570565900109</v>
+      </c>
+      <c r="I49" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J49" s="5" t="n">
+        <v>-199.065316647012</v>
+      </c>
+      <c r="K49" s="5" t="n">
+        <v>11.5897266</v>
+      </c>
+      <c r="L49" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M49" s="5" t="n">
+        <v>104.130213067165</v>
+      </c>
+      <c r="N49" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F50" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="G50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" s="5" t="n">
+        <v>-69.7138420354356</v>
+      </c>
+      <c r="I50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L50" s="5" t="n">
+        <v>-12.9350691</v>
+      </c>
+      <c r="M50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N50" s="5" t="n">
+        <v>-52.6020315960714</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F51" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="G51" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" s="5" t="n">
+        <v>-27.3575205630524</v>
+      </c>
+      <c r="I51" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J51" s="5" t="n">
+        <v>-16.9182</v>
+      </c>
+      <c r="K51" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L51" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M51" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N51" s="5" t="n">
+        <v>-8.80025888258852</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F52" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="G52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H52" s="5" t="n">
+        <v>-0.771437819347626</v>
+      </c>
+      <c r="I52" s="5" t="n">
+        <v>0.732</v>
+      </c>
+      <c r="J52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L52" s="5" t="n">
+        <v>-12.081843</v>
+      </c>
+      <c r="M52" s="5" t="n">
+        <v>10.6246240682761</v>
+      </c>
+      <c r="N52" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F53" s="0" t="s">
+        <v>27</v>
+      </c>
+      <c r="G53" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H53" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I53" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J53" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K53" s="5" t="n">
+        <v>10.8095706</v>
+      </c>
+      <c r="L53" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M53" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N53" s="5" t="n">
+        <v>-10.8095705999999</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F54" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="G54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K54" s="5" t="n">
+        <v>9.25891965</v>
+      </c>
+      <c r="L54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N54" s="5" t="n">
         <v>-9.25891964999985</v>
       </c>
     </row>
